--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488020_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488020_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>13.1587</v>
+        <v>13.9476</v>
       </c>
       <c r="E2" t="n">
-        <v>12.7386</v>
+        <v>13.7802</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4202</v>
+        <v>0.1675</v>
       </c>
       <c r="G2" t="n">
         <v>7.3565</v>
@@ -610,13 +610,13 @@
         <v>2.9733</v>
       </c>
       <c r="S2" t="n">
-        <v>1.3108</v>
+        <v>2.0997</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0772</v>
+        <v>1.1188</v>
       </c>
       <c r="U2" t="n">
-        <v>1.2336</v>
+        <v>0.9809</v>
       </c>
       <c r="V2" t="n">
         <v>4.4914</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.8999</v>
+        <v>8.117000000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>5.8022</v>
+        <v>6.2721</v>
       </c>
       <c r="F3" t="n">
-        <v>2.0977</v>
+        <v>1.845</v>
       </c>
       <c r="G3" t="n">
         <v>3.8484</v>
@@ -688,13 +688,13 @@
         <v>2.9733</v>
       </c>
       <c r="S3" t="n">
-        <v>2.3864</v>
+        <v>2.6035</v>
       </c>
       <c r="T3" t="n">
-        <v>1.017</v>
+        <v>1.4868</v>
       </c>
       <c r="U3" t="n">
-        <v>1.3694</v>
+        <v>1.1167</v>
       </c>
       <c r="V3" t="n">
         <v>0.674</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. HETOR MENSAH</t>
+          <t>A. DIAZ ROLLANO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.935</v>
+        <v>4.9971</v>
       </c>
       <c r="E4" t="n">
-        <v>5.3436</v>
+        <v>5.0196</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5913</v>
+        <v>-0.0225</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8497</v>
+        <v>0.4477</v>
       </c>
       <c r="H4" t="n">
-        <v>2.5887</v>
+        <v>0.2717</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.739</v>
+        <v>0.176</v>
       </c>
       <c r="J4" t="n">
-        <v>3.035</v>
+        <v>2.1032</v>
       </c>
       <c r="K4" t="n">
-        <v>3.5858</v>
+        <v>0.7333</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.5508</v>
+        <v>1.3699</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.1853</v>
+        <v>-1.6556</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.9971</v>
+        <v>-0.4617</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.1882</v>
+        <v>-1.1939</v>
       </c>
       <c r="P4" t="n">
-        <v>1.5858</v>
+        <v>2.5769</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>2.5769</v>
       </c>
       <c r="S4" t="n">
-        <v>4.44</v>
+        <v>0.7654</v>
       </c>
       <c r="T4" t="n">
-        <v>3.3701</v>
+        <v>0.5021</v>
       </c>
       <c r="U4" t="n">
-        <v>1.0699</v>
+        <v>0.2633</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.9405</v>
+        <v>1.2071</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.0704</v>
+        <v>2.4142</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.8701</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. DIAZ ROLLANO</t>
+          <t>A. ARTILES AGUILAR</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>5.1997</v>
+        <v>4.6484</v>
       </c>
       <c r="E5" t="n">
-        <v>5.138</v>
+        <v>3.695</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0617</v>
+        <v>0.9534</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4477</v>
+        <v>1.9396</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2717</v>
+        <v>1.0881</v>
       </c>
       <c r="I5" t="n">
-        <v>0.176</v>
+        <v>0.8515</v>
       </c>
       <c r="J5" t="n">
-        <v>2.1032</v>
+        <v>3.4611</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7333</v>
+        <v>2.3608</v>
       </c>
       <c r="L5" t="n">
-        <v>1.3699</v>
+        <v>1.1004</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.6556</v>
+        <v>-1.5215</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4617</v>
+        <v>-1.2727</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.1939</v>
+        <v>-0.2488</v>
       </c>
       <c r="P5" t="n">
-        <v>2.5769</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.9822</v>
       </c>
       <c r="R5" t="n">
-        <v>2.5769</v>
+        <v>1.9822</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9681</v>
+        <v>1.5721</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6205000000000001</v>
+        <v>1.0794</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3475</v>
+        <v>0.4927</v>
       </c>
       <c r="V5" t="n">
-        <v>1.2071</v>
+        <v>1.1367</v>
       </c>
       <c r="W5" t="n">
-        <v>2.4142</v>
+        <v>1.1367</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2071</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. ARTILES AGUILAR</t>
+          <t>M. HETOR MENSAH</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>4.2771</v>
+        <v>4.0462</v>
       </c>
       <c r="E6" t="n">
-        <v>3.6326</v>
+        <v>3.5953</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6445</v>
+        <v>0.4509</v>
       </c>
       <c r="G6" t="n">
-        <v>1.9396</v>
+        <v>0.8497</v>
       </c>
       <c r="H6" t="n">
-        <v>1.0881</v>
+        <v>2.5887</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8515</v>
+        <v>-1.739</v>
       </c>
       <c r="J6" t="n">
-        <v>3.4611</v>
+        <v>3.035</v>
       </c>
       <c r="K6" t="n">
-        <v>2.3608</v>
+        <v>3.5858</v>
       </c>
       <c r="L6" t="n">
-        <v>1.1004</v>
+        <v>-0.5508</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.5215</v>
+        <v>-2.1853</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.2727</v>
+        <v>-0.9971</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2488</v>
+        <v>-1.1882</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.5858</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.9822</v>
+        <v>-0.9911</v>
       </c>
       <c r="R6" t="n">
-        <v>1.9822</v>
+        <v>2.5769</v>
       </c>
       <c r="S6" t="n">
-        <v>1.2008</v>
+        <v>2.5513</v>
       </c>
       <c r="T6" t="n">
-        <v>1.017</v>
+        <v>1.6218</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1838</v>
+        <v>0.9295</v>
       </c>
       <c r="V6" t="n">
-        <v>1.1367</v>
+        <v>-0.9405</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1367</v>
+        <v>-0.0704</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.8701</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3335</v>
+        <v>0.5829</v>
       </c>
       <c r="E7" t="n">
-        <v>1.0086</v>
+        <v>1.3142</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.6751</v>
+        <v>-0.7313</v>
       </c>
       <c r="G7" t="n">
         <v>-0.8787</v>
@@ -1000,13 +1000,13 @@
         <v>0.3964</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2122</v>
+        <v>0.4616</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1872</v>
+        <v>0.1184</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3993</v>
+        <v>0.3432</v>
       </c>
       <c r="V7" t="n">
         <v>0.6036</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2561</v>
+        <v>-0.1999</v>
       </c>
       <c r="E9" t="n">
         <v>-0.0222</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2338</v>
+        <v>-0.1777</v>
       </c>
       <c r="G9" t="n">
         <v>-0.2935</v>
@@ -1156,13 +1156,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0374</v>
+        <v>0.0936</v>
       </c>
       <c r="T9" t="n">
         <v>-0.0624</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0998</v>
+        <v>0.156</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.9911</v>
+        <v>-0.3194</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.2868</v>
+        <v>0.1041</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.7043</v>
+        <v>-0.4235</v>
       </c>
       <c r="G10" t="n">
         <v>-1.8104</v>
@@ -1234,13 +1234,13 @@
         <v>1.9822</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0441</v>
+        <v>0.7158</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0038</v>
+        <v>0.3947</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0403</v>
+        <v>0.3211</v>
       </c>
       <c r="V10" t="n">
         <v>-1.2071</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.5932</v>
+        <v>-1.1586</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.342</v>
+        <v>-0.0759</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.2512</v>
+        <v>-1.0827</v>
       </c>
       <c r="G11" t="n">
         <v>-1.0218</v>
@@ -1312,13 +1312,13 @@
         <v>1.1893</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0499</v>
+        <v>0.4845</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0955</v>
+        <v>0.3616</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0456</v>
+        <v>0.1229</v>
       </c>
       <c r="V11" t="n">
         <v>-1.8107</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.0876</v>
+        <v>-2.3422</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.3971</v>
+        <v>-1.6798</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.6905</v>
+        <v>-0.6624</v>
       </c>
       <c r="G12" t="n">
         <v>-4.2171</v>
@@ -1390,13 +1390,13 @@
         <v>1.3876</v>
       </c>
       <c r="S12" t="n">
-        <v>0.742</v>
+        <v>0.4874</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4847</v>
+        <v>0.202</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2573</v>
+        <v>0.2854</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.1542</v>
+        <v>-3.0847</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.1715</v>
+        <v>-1.9053</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.9828</v>
+        <v>-1.1793</v>
       </c>
       <c r="G13" t="n">
         <v>-1.007</v>
@@ -1468,13 +1468,13 @@
         <v>0.1982</v>
       </c>
       <c r="S13" t="n">
-        <v>0.1699</v>
+        <v>0.2395</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2496</v>
+        <v>0.0165</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4195</v>
+        <v>0.223</v>
       </c>
       <c r="V13" t="n">
         <v>-0.5331</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-4.498</v>
+        <v>-3.7629</v>
       </c>
       <c r="E14" t="n">
-        <v>-4.4079</v>
+        <v>-3.8132</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.0901</v>
+        <v>0.0503</v>
       </c>
       <c r="G14" t="n">
         <v>-3.623</v>
@@ -1546,13 +1546,13 @@
         <v>2.5769</v>
       </c>
       <c r="S14" t="n">
-        <v>0.6076</v>
+        <v>1.3427</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2754</v>
+        <v>0.8701</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3322</v>
+        <v>0.4725</v>
       </c>
       <c r="V14" t="n">
         <v>-2.0772</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>24.52639999999999</v>
+        <v>25.77419999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>25.3388</v>
+        <v>26.5868</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.8124000000000001</v>
+        <v>-0.8122999999999992</v>
       </c>
       <c r="G15" t="n">
         <v>1.893099999999998</v>
@@ -1624,13 +1624,13 @@
         <v>20.8132</v>
       </c>
       <c r="S15" t="n">
-        <v>12.1692</v>
+        <v>13.4171</v>
       </c>
       <c r="T15" t="n">
-        <v>6.462000000000001</v>
+        <v>7.7098</v>
       </c>
       <c r="U15" t="n">
-        <v>5.707</v>
+        <v>5.7072</v>
       </c>
       <c r="V15" t="n">
         <v>1.5442</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. PEREZ SARRABLO</t>
+          <t>A. BUALO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.66</v>
+        <v>2.6671</v>
       </c>
       <c r="E16" t="n">
-        <v>3.6727</v>
+        <v>6.1828</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.0126</v>
+        <v>-3.5157</v>
       </c>
       <c r="G16" t="n">
-        <v>4.4141</v>
+        <v>1.6968</v>
       </c>
       <c r="H16" t="n">
-        <v>1.816</v>
+        <v>0.2027</v>
       </c>
       <c r="I16" t="n">
-        <v>2.5981</v>
+        <v>1.4941</v>
       </c>
       <c r="J16" t="n">
-        <v>5.7246</v>
+        <v>4.1966</v>
       </c>
       <c r="K16" t="n">
-        <v>1.2648</v>
+        <v>1.6615</v>
       </c>
       <c r="L16" t="n">
-        <v>4.4597</v>
+        <v>2.5351</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.3105</v>
+        <v>-2.4998</v>
       </c>
       <c r="N16" t="n">
-        <v>0.5512</v>
+        <v>-1.4588</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.8617</v>
+        <v>-1.041</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.1982</v>
+        <v>-0.7929</v>
       </c>
       <c r="Q16" t="n">
         <v>-1.9822</v>
       </c>
       <c r="R16" t="n">
-        <v>1.784</v>
+        <v>1.1893</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.228</v>
+        <v>-1.2546</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0696</v>
+        <v>-0.523</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1583</v>
+        <v>-0.7316</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.3278</v>
+        <v>3.0178</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>4.4914</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.3278</v>
+        <v>-1.4737</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. BUALO</t>
+          <t>M. PEREZ SARRABLO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.5711</v>
+        <v>2.3264</v>
       </c>
       <c r="E17" t="n">
-        <v>6.3866</v>
+        <v>3.3671</v>
       </c>
       <c r="F17" t="n">
-        <v>-3.8155</v>
+        <v>-1.0407</v>
       </c>
       <c r="G17" t="n">
-        <v>1.6968</v>
+        <v>4.4141</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2027</v>
+        <v>1.816</v>
       </c>
       <c r="I17" t="n">
-        <v>1.4941</v>
+        <v>2.5981</v>
       </c>
       <c r="J17" t="n">
-        <v>4.1966</v>
+        <v>5.7246</v>
       </c>
       <c r="K17" t="n">
-        <v>1.6615</v>
+        <v>1.2648</v>
       </c>
       <c r="L17" t="n">
-        <v>2.5351</v>
+        <v>4.4597</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.4998</v>
+        <v>-1.3105</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.4588</v>
+        <v>0.5512</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.041</v>
+        <v>-1.8617</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.7929</v>
+        <v>-0.1982</v>
       </c>
       <c r="Q17" t="n">
         <v>-1.9822</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1893</v>
+        <v>1.784</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.3506</v>
+        <v>-0.5617</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3192</v>
+        <v>-0.3752</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.0313</v>
+        <v>-0.1864</v>
       </c>
       <c r="V17" t="n">
-        <v>3.0178</v>
+        <v>-1.3278</v>
       </c>
       <c r="W17" t="n">
-        <v>4.4914</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.4737</v>
+        <v>-1.3278</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6107</v>
+        <v>0.5754</v>
       </c>
       <c r="E18" t="n">
-        <v>1.003</v>
+        <v>0.3918</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.3924</v>
+        <v>0.1836</v>
       </c>
       <c r="G18" t="n">
         <v>0.0464</v>
@@ -1858,13 +1858,13 @@
         <v>1.1893</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2621</v>
+        <v>-0.2973</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4847</v>
+        <v>-0.1265</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.7468</v>
+        <v>-0.1708</v>
       </c>
       <c r="V18" t="n">
         <v>2.6104</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2045</v>
+        <v>0.2326</v>
       </c>
       <c r="E20" t="n">
         <v>0.176</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0285</v>
+        <v>0.0566</v>
       </c>
       <c r="G20" t="n">
         <v>0.09719999999999999</v>
@@ -2014,13 +2014,13 @@
         <v>0.3964</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1685</v>
+        <v>-0.1404</v>
       </c>
       <c r="T20" t="n">
         <v>-0.1872</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0187</v>
+        <v>0.0468</v>
       </c>
       <c r="V20" t="n">
         <v>-0.1207</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.6553</v>
+        <v>-0.4692</v>
       </c>
       <c r="E21" t="n">
-        <v>0.6195000000000001</v>
+        <v>0.7214</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.2748</v>
+        <v>-1.1906</v>
       </c>
       <c r="G21" t="n">
         <v>-0.466</v>
@@ -2092,13 +2092,13 @@
         <v>0.5947</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6633</v>
+        <v>-0.4772</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.312</v>
+        <v>-0.2101</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3513</v>
+        <v>-0.2671</v>
       </c>
       <c r="V21" t="n">
         <v>-0.1207</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.4469</v>
+        <v>-0.9329</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.274</v>
+        <v>-1.1721</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.1729</v>
+        <v>0.2392</v>
       </c>
       <c r="G22" t="n">
         <v>-0.9808</v>
@@ -2170,13 +2170,13 @@
         <v>1.1893</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.1471</v>
+        <v>-0.6332</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.624</v>
+        <v>-0.5221</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5231</v>
+        <v>-0.1111</v>
       </c>
       <c r="V22" t="n">
         <v>0.4828</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>R. CABARROCAS MARTIN</t>
+          <t>D. GARZON ALVAREZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.2303</v>
+        <v>-2.5515</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.7468</v>
+        <v>0.5163</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.4836</v>
+        <v>-3.0678</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.0475</v>
+        <v>0.4744</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.8637</v>
+        <v>-0.3942</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.1838</v>
+        <v>0.8686</v>
       </c>
       <c r="J23" t="n">
-        <v>0.8683</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.5379</v>
+        <v>-0.6117</v>
       </c>
       <c r="L23" t="n">
-        <v>1.4062</v>
+        <v>1.2533</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.9158</v>
+        <v>-0.1672</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.3258</v>
+        <v>0.2175</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.59</v>
+        <v>-0.3847</v>
       </c>
       <c r="P23" t="n">
-        <v>0.1982</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1893</v>
+        <v>0.9911</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.174</v>
+        <v>-0.3451</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.624</v>
+        <v>-0.3413</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.55</v>
+        <v>-0.0038</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.2071</v>
+        <v>-2.6808</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.2071</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.2071</v>
+        <v>-3.8879</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>D. GARZON ALVAREZ</t>
+          <t>R. CABARROCAS MARTIN</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.3664</v>
+        <v>-2.9705</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1088</v>
+        <v>-0.543</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.4752</v>
+        <v>-2.4274</v>
       </c>
       <c r="G24" t="n">
-        <v>0.4744</v>
+        <v>-1.0475</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.3942</v>
+        <v>-0.8637</v>
       </c>
       <c r="I24" t="n">
-        <v>0.8686</v>
+        <v>-0.1838</v>
       </c>
       <c r="J24" t="n">
-        <v>0.6415999999999999</v>
+        <v>0.8683</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.6117</v>
+        <v>-0.5379</v>
       </c>
       <c r="L24" t="n">
-        <v>1.2533</v>
+        <v>1.4062</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.1672</v>
+        <v>-1.9158</v>
       </c>
       <c r="N24" t="n">
-        <v>0.2175</v>
+        <v>-0.3258</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.3847</v>
+        <v>-1.59</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>0.1982</v>
       </c>
       <c r="Q24" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R24" t="n">
-        <v>0.9911</v>
+        <v>1.1893</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.16</v>
+        <v>-0.9141</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.7488</v>
+        <v>-0.4202</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4113</v>
+        <v>-0.4938</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.6808</v>
+        <v>-1.2071</v>
       </c>
       <c r="W24" t="n">
-        <v>1.2071</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-3.8879</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.2052</v>
+        <v>-3.6913</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.181</v>
+        <v>-1.0792</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.0241</v>
+        <v>-2.6121</v>
       </c>
       <c r="G25" t="n">
         <v>-1.9655</v>
@@ -2404,13 +2404,13 @@
         <v>0.9911</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.9731</v>
+        <v>-1.4592</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.8112</v>
+        <v>-0.7093</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.1619</v>
+        <v>-0.7499</v>
       </c>
       <c r="V25" t="n">
         <v>-0.2666</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-4.6371</v>
+        <v>-4.7605</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.03</v>
+        <v>-1.8262</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.6071</v>
+        <v>-2.9342</v>
       </c>
       <c r="G26" t="n">
         <v>-1.6813</v>
@@ -2482,13 +2482,13 @@
         <v>1.1893</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.0064</v>
+        <v>-1.1298</v>
       </c>
       <c r="T26" t="n">
-        <v>-1.1232</v>
+        <v>-0.9194</v>
       </c>
       <c r="U26" t="n">
-        <v>0.1168</v>
+        <v>-0.2104</v>
       </c>
       <c r="V26" t="n">
         <v>-2.1476</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-5.5374</v>
+        <v>-5.4016</v>
       </c>
       <c r="E27" t="n">
         <v>-2.2837</v>
       </c>
       <c r="F27" t="n">
-        <v>-3.2536</v>
+        <v>-3.1178</v>
       </c>
       <c r="G27" t="n">
         <v>-0.8771</v>
@@ -2560,13 +2560,13 @@
         <v>0.7929</v>
       </c>
       <c r="S27" t="n">
-        <v>-1.2224</v>
+        <v>-1.0866</v>
       </c>
       <c r="T27" t="n">
         <v>-0.6864</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.5361</v>
+        <v>-0.4002</v>
       </c>
       <c r="V27" t="n">
         <v>-1.2574</v>
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-7.7968</v>
+        <v>-7.1366</v>
       </c>
       <c r="E28" t="n">
         <v>-5.1486</v>
       </c>
       <c r="F28" t="n">
-        <v>-2.6482</v>
+        <v>-1.988</v>
       </c>
       <c r="G28" t="n">
         <v>-1.9064</v>
@@ -2638,13 +2638,13 @@
         <v>0.3964</v>
       </c>
       <c r="S28" t="n">
-        <v>-1.8138</v>
+        <v>-1.1536</v>
       </c>
       <c r="T28" t="n">
         <v>-0.6864</v>
       </c>
       <c r="U28" t="n">
-        <v>-1.1274</v>
+        <v>-0.4672</v>
       </c>
       <c r="V28" t="n">
         <v>1.4737</v>
@@ -2671,13 +2671,13 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>-24.5264</v>
+        <v>-21.8099</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.3947999999999965</v>
+        <v>-0.3946999999999985</v>
       </c>
       <c r="F29" t="n">
-        <v>-24.1315</v>
+        <v>-21.4149</v>
       </c>
       <c r="G29" t="n">
         <v>-1.892999999999999</v>
@@ -2695,7 +2695,7 @@
         <v>7.3134</v>
       </c>
       <c r="L29" t="n">
-        <v>7.893000000000001</v>
+        <v>7.892999999999999</v>
       </c>
       <c r="M29" t="n">
         <v>-17.0995</v>
@@ -2716,13 +2716,13 @@
         <v>11.8931</v>
       </c>
       <c r="S29" t="n">
-        <v>-12.1693</v>
+        <v>-9.4528</v>
       </c>
       <c r="T29" t="n">
-        <v>-5.707299999999999</v>
+        <v>-5.707100000000001</v>
       </c>
       <c r="U29" t="n">
-        <v>-6.462000000000001</v>
+        <v>-3.7455</v>
       </c>
       <c r="V29" t="n">
         <v>-1.544</v>
